--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.84091755476697</v>
+        <v>5.336649102649632</v>
       </c>
       <c r="D2" t="n">
-        <v>32.11546693160241</v>
+        <v>5.218763376385392</v>
       </c>
       <c r="E2" t="n">
-        <v>6.577552956123408</v>
+        <v>1.068852355370054</v>
       </c>
       <c r="F2" t="n">
-        <v>6.68129488734385</v>
+        <v>1.085710419193376</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.7267957237566</v>
+        <v>7.430604305110448</v>
       </c>
       <c r="D3" t="n">
-        <v>44.66949815925498</v>
+        <v>7.258793450878934</v>
       </c>
       <c r="E3" t="n">
-        <v>6.577552956123408</v>
+        <v>1.068852355370054</v>
       </c>
       <c r="F3" t="n">
-        <v>6.68129488734385</v>
+        <v>1.085710419193376</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.94541568808554</v>
+        <v>4.378630049313901</v>
       </c>
       <c r="D4" t="n">
-        <v>25.98168588101437</v>
+        <v>4.222023955664836</v>
       </c>
       <c r="E4" t="n">
-        <v>6.577552956123408</v>
+        <v>1.068852355370054</v>
       </c>
       <c r="F4" t="n">
-        <v>6.68129488734385</v>
+        <v>1.085710419193376</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.36905376845693</v>
+        <v>6.397471237374251</v>
       </c>
       <c r="D5" t="n">
-        <v>39.87090479958074</v>
+        <v>6.479022029931871</v>
       </c>
       <c r="E5" t="n">
-        <v>6.577552956123408</v>
+        <v>1.068852355370054</v>
       </c>
       <c r="F5" t="n">
-        <v>6.68129488734385</v>
+        <v>1.085710419193376</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.40012055420576</v>
+        <v>5.102519590058437</v>
       </c>
       <c r="D6" t="n">
-        <v>30.90777695582031</v>
+        <v>5.0225137553208</v>
       </c>
       <c r="E6" t="n">
-        <v>6.577552956123408</v>
+        <v>1.068852355370054</v>
       </c>
       <c r="F6" t="n">
-        <v>6.68129488734385</v>
+        <v>1.085710419193376</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
